--- a/rapporten/prijsrapport-NL-2026-05-06.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
   <si>
     <t>Product</t>
   </si>
@@ -37,142 +37,268 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
-    <t>1692530</t>
+    <t>Juwelium</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658999430</t>
   </si>
   <si>
-    <t>1840300</t>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>8715658380931</t>
   </si>
   <si>
+    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658370086</t>
   </si>
   <si>
+    <t>Omerta - Golden challenge EDT men 100 ml</t>
+  </si>
+  <si>
     <t>8720938379345</t>
   </si>
   <si>
+    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380351</t>
   </si>
   <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370505</t>
   </si>
   <si>
+    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380221</t>
   </si>
   <si>
+    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8720938379352</t>
   </si>
   <si>
+    <t>Omerta - Royal X Red - EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370369</t>
   </si>
   <si>
+    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658999638</t>
   </si>
   <si>
+    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370543</t>
   </si>
   <si>
+    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380757</t>
   </si>
   <si>
+    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380405</t>
   </si>
   <si>
+    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380672</t>
   </si>
   <si>
+    <t>Omerta - Sensible Man - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658999249</t>
   </si>
   <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380115</t>
   </si>
   <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658998839</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658997993</t>
   </si>
   <si>
+    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380665</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Elixer - 1EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370437</t>
   </si>
   <si>
+    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380658</t>
   </si>
   <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658370062</t>
   </si>
   <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
     <t>8715658380580</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494225</t>
   </si>
   <si>
-    <t>946246</t>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
     <t>8721055494263</t>
   </si>
   <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816691</t>
   </si>
   <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816653</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494270</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494232</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816714</t>
   </si>
   <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816615</t>
   </si>
   <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493211</t>
   </si>
   <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816790</t>
   </si>
   <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816837</t>
   </si>
   <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816813</t>
   </si>
   <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493198</t>
   </si>
   <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493228</t>
   </si>
   <si>
+    <t>Creation Lamis Fatal Snake Magical Giftset</t>
+  </si>
+  <si>
     <t>6291012871731</t>
   </si>
   <si>
-    <t>1762224</t>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Creation Lamis Golden Wave for Men Giftset</t>
   </si>
   <si>
     <t>6291012002661</t>
@@ -611,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>9.95</v>
@@ -623,21 +749,21 @@
         <v>0.47</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>9.48</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>9.79</v>
@@ -649,21 +775,21 @@
         <v>0.29</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
         <v>9.5</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>9.79</v>
@@ -675,21 +801,21 @@
         <v>0.29</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
         <v>9.5</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>9.79</v>
@@ -701,21 +827,21 @@
         <v>0.29</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
         <v>9.5</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>9.79</v>
@@ -727,21 +853,21 @@
         <v>0.29</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
         <v>9.5</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>9.79</v>
@@ -753,21 +879,21 @@
         <v>0.29</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
         <v>9.5</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>9.79</v>
@@ -779,21 +905,21 @@
         <v>0.29</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
         <v>9.5</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>9.79</v>
@@ -805,21 +931,21 @@
         <v>0.29</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
         <v>9.5</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>9.79</v>
@@ -831,21 +957,21 @@
         <v>0.29</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
         <v>9.5</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1">
         <v>9.79</v>
@@ -857,21 +983,21 @@
         <v>0.29</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
         <v>9.5</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>9.79</v>
@@ -883,21 +1009,21 @@
         <v>0.29</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
         <v>9.5</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1">
         <v>9.79</v>
@@ -909,21 +1035,21 @@
         <v>0.29</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
         <v>9.5</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1">
         <v>9.79</v>
@@ -935,21 +1061,21 @@
         <v>0.29</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
         <v>9.5</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1">
         <v>9.79</v>
@@ -961,21 +1087,21 @@
         <v>0.29</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
         <v>9.5</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1">
         <v>9.79</v>
@@ -987,21 +1113,21 @@
         <v>0.29</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
         <v>9.5</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1">
         <v>9.79</v>
@@ -1013,21 +1139,21 @@
         <v>0.29</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
         <v>9.5</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1">
         <v>9.79</v>
@@ -1039,21 +1165,21 @@
         <v>0.29</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
         <v>9.5</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1">
         <v>9.79</v>
@@ -1065,21 +1191,21 @@
         <v>0.29</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
         <v>9.5</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1">
         <v>9.79</v>
@@ -1091,21 +1217,21 @@
         <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
         <v>9.5</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1">
         <v>9.79</v>
@@ -1117,21 +1243,21 @@
         <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
         <v>9.5</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1">
         <v>9.79</v>
@@ -1143,21 +1269,21 @@
         <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1">
         <v>9.5</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1">
         <v>9.79</v>
@@ -1169,21 +1295,21 @@
         <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1">
         <v>9.5</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1">
         <v>9.79</v>
@@ -1195,21 +1321,21 @@
         <v>0.29</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1">
         <v>9.5</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1">
         <v>9.79</v>
@@ -1221,21 +1347,21 @@
         <v>0.29</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="1">
         <v>9.5</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1">
         <v>5.25</v>
@@ -1247,21 +1373,21 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1">
         <v>5.25</v>
@@ -1273,21 +1399,21 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1">
         <v>5.25</v>
@@ -1299,21 +1425,21 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1">
         <v>5.25</v>
@@ -1325,21 +1451,21 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>5.25</v>
@@ -1351,21 +1477,21 @@
         <v>0.26</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G30" s="1">
         <v>4.99</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1">
         <v>5.25</v>
@@ -1377,21 +1503,21 @@
         <v>0.26</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G31" s="1">
         <v>4.99</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1">
         <v>5.25</v>
@@ -1403,21 +1529,21 @@
         <v>0.26</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G32" s="1">
         <v>4.99</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1">
         <v>5.25</v>
@@ -1429,21 +1555,21 @@
         <v>0.26</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1">
         <v>4.99</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C34" s="1">
         <v>5.25</v>
@@ -1455,21 +1581,21 @@
         <v>0.26</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G34" s="1">
         <v>4.99</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>5.25</v>
@@ -1481,21 +1607,21 @@
         <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G35" s="1">
         <v>4.99</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1">
         <v>5.25</v>
@@ -1507,21 +1633,21 @@
         <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G36" s="1">
         <v>4.99</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C37" s="1">
         <v>5.25</v>
@@ -1533,21 +1659,21 @@
         <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G37" s="1">
         <v>4.99</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1">
         <v>5.25</v>
@@ -1559,21 +1685,21 @@
         <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G38" s="1">
         <v>4.99</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C39" s="1">
         <v>5.25</v>
@@ -1585,21 +1711,21 @@
         <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G39" s="1">
         <v>4.99</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1">
         <v>5.25</v>
@@ -1611,21 +1737,21 @@
         <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G40" s="1">
         <v>4.99</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1">
         <v>5.25</v>
@@ -1637,21 +1763,21 @@
         <v>0.26</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G41" s="1">
         <v>4.99</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1">
         <v>13.69</v>
@@ -1663,21 +1789,21 @@
         <v>0.06</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="G42" s="1">
         <v>13.63</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>12.69</v>
@@ -1689,13 +1815,13 @@
         <v>0.03</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="G43" s="1">
         <v>12.66</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/prijsrapport-NL-2026-05-06.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-06.xlsx
@@ -740,13 +740,13 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>9.95</v>
+        <v>9.94</v>
       </c>
       <c r="D2" s="1">
         <v>9.48</v>
       </c>
       <c r="E2" s="1">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
